--- a/output/pdf_financials_xlsx/PRS.H.xlsx
+++ b/output/pdf_financials_xlsx/PRS.H.xlsx
@@ -6532,43 +6532,43 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.40668</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.40668</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.40668</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.40668</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.60361</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.630863</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.630863</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.630863</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.630863</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.924834</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.924834</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.924834</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.924834</v>
       </c>
     </row>
     <row r="93">
@@ -10808,7 +10808,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -12032,7 +12036,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13080,7 +13088,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -14368,7 +14380,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15716,7 +15732,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PRS.H.xlsx
+++ b/output/pdf_financials_xlsx/PRS.H.xlsx
@@ -1027,10 +1027,10 @@
         <v>0.017861</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.029716</v>
+        <v>0.06784999999999999</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.045732</v>
+        <v>0.080854</v>
       </c>
     </row>
     <row r="11">
@@ -1097,7 +1097,7 @@
         <v>-0.06784999999999999</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>-0.045732</v>
+        <v>-0.080854</v>
       </c>
     </row>
     <row r="12">
@@ -1131,19 +1131,19 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.004181</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.004986</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.004313</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001413</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2218,19 +2218,19 @@
         <v>-0.497484</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.056998</v>
+        <v>-0.061179</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.070563</v>
+        <v>-0.07554900000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.138723</v>
+        <v>-0.143036</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.405058</v>
+        <v>-1.406471</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.356704</v>
+        <v>-1.356708</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.835366</v>
@@ -2352,19 +2352,19 @@
         <v>-0.497484</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.056998</v>
+        <v>-0.061179</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.070563</v>
+        <v>-0.07554900000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.138723</v>
+        <v>-0.143036</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.404043</v>
+        <v>-1.405456</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.354875</v>
+        <v>-1.354879</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.834033</v>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002036</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001418</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -2695,28 +2695,28 @@
         <v>0.630582</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.027225</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.022219</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.043872</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.092222</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.058789</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.030381</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.019718</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.002763</v>
       </c>
     </row>
     <row r="35">
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002036</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001418</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -2821,28 +2821,28 @@
         <v>0.631182</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0098</v>
+        <v>0.037025</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.0074</v>
+        <v>0.029619</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.043872</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.092222</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.058789</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.030381</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.019718</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.002763</v>
       </c>
     </row>
     <row r="37">
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002418</v>
+        <v>0.000382</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.0018</v>
+        <v>0.000382</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.00203</v>
@@ -3577,25 +3577,25 @@
         <v>0.032061</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.047335</v>
+        <v>0.02011</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.060453</v>
+        <v>0.038234</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.043872</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.097457</v>
+        <v>0.005235</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.064443</v>
+        <v>0.005654</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.031631</v>
+        <v>0.00125</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.020968</v>
+        <v>0.00125</v>
       </c>
       <c r="S48" s="3" t="n">
         <v>0</v>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19384,7 +19384,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -32662,10 +32662,10 @@
         </is>
       </c>
       <c r="U219" s="5" t="n">
-        <v>-0.06784999999999999</v>
+        <v>0.06784999999999999</v>
       </c>
       <c r="V219" s="5" t="n">
-        <v>-0.080854</v>
+        <v>0.080854</v>
       </c>
     </row>
     <row r="220">
@@ -32790,7 +32790,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -38628,7 +38628,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -39786,7 +39786,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -41272,7 +41272,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -42532,7 +42532,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
